--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A028A331-29F5-DA46-9128-05B3DBC8B48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E83072B-B24D-A446-A7F4-332781774811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31280" yWindow="-4140" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="218">
   <si>
     <t>Year</t>
   </si>
@@ -703,6 +703,30 @@
   </si>
   <si>
     <t>Dixit, A., Najibi, N., Mishra, N., Dixit, J., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <t>La Niña- and El Niño-like Long-Term Sea Surface Temperature Trends Modulate Atmospheric River Activity in Western North America</t>
+  </si>
+  <si>
+    <t>Kwong A., Dixit A., Lehner F.</t>
+  </si>
+  <si>
+    <t>106th Annual Meeting of the American Meteorological Society (AMS)</t>
+  </si>
+  <si>
+    <t>Houston, Texas, 25–29 January 2026</t>
+  </si>
+  <si>
+    <t>Dixit A., Musselman K. N., Addor N., Carr S., Gutmann E., Huang L., Minder J. R., Newman A. J., Petach T., Rahimi S., Vano J. A., Lehner F.</t>
+  </si>
+  <si>
+    <t>Resolving snow refugia delays climate change emergence in mountain snowpack</t>
+  </si>
+  <si>
+    <t>Kwong A., Dixit A., Shields C. A., Lehner F.</t>
+  </si>
+  <si>
+    <t>Competing influences of external forcing and sea surface temperature trends on North Pacific atmospheric rivers</t>
   </si>
 </sst>
 </file>
@@ -860,7 +884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -896,6 +920,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1108,10 +1135,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I58" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="A1:I58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I42">
-    <sortCondition ref="C1:C42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I62" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:I62" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I46">
+    <sortCondition ref="C1:C46"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="8"/>
@@ -1323,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" customWidth="1"/>
@@ -1417,22 +1444,42 @@
       <c r="H6" s="4"/>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="9"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+    <row r="7" spans="1:9" ht="34">
+      <c r="A7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="9"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+    <row r="8" spans="1:9" ht="51">
+      <c r="A8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>214</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="10"/>
@@ -1505,125 +1552,67 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="68">
-      <c r="A12" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="34">
-      <c r="A13" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="34">
-      <c r="A14" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="34">
+    <row r="12" spans="1:9">
+      <c r="A12" s="9"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="9"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="9"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" ht="51">
       <c r="A15" s="4">
         <v>2026</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>21</v>
+        <v>211</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="34">
+        <v>213</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" spans="1:9" ht="68">
       <c r="A16" s="4">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -1632,19 +1621,19 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>24</v>
+        <v>69</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>13</v>
@@ -1652,7 +1641,7 @@
     </row>
     <row r="17" spans="1:9" ht="34">
       <c r="A17" s="4">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
@@ -1661,27 +1650,27 @@
         <v>15</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="51">
+    <row r="18" spans="1:9" ht="34">
       <c r="A18" s="4">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>14</v>
@@ -1690,19 +1679,19 @@
         <v>15</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>13</v>
@@ -1710,7 +1699,7 @@
     </row>
     <row r="19" spans="1:9" ht="34">
       <c r="A19" s="4">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
@@ -1719,19 +1708,19 @@
         <v>15</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>13</v>
@@ -1739,7 +1728,7 @@
     </row>
     <row r="20" spans="1:9" ht="34">
       <c r="A20" s="4">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>14</v>
@@ -1748,19 +1737,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>13</v>
@@ -1768,7 +1757,7 @@
     </row>
     <row r="21" spans="1:9" ht="34">
       <c r="A21" s="4">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
@@ -1777,143 +1766,143 @@
         <v>15</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="51">
-      <c r="A22" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
+      <c r="D22" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="34">
-      <c r="A23" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>41</v>
+      <c r="D23" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="34">
-      <c r="A24" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>44</v>
+      <c r="D24" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="34">
-      <c r="A25" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>46</v>
+      <c r="D25" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="68">
+        <v>89</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="51">
       <c r="A26" s="2">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>14</v>
@@ -1922,19 +1911,19 @@
         <v>15</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>13</v>
@@ -1942,7 +1931,7 @@
     </row>
     <row r="27" spans="1:9" ht="34">
       <c r="A27" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>14</v>
@@ -1951,236 +1940,244 @@
         <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="34">
+      <c r="A28" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="51">
-      <c r="A28" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="F28" s="6" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="34">
       <c r="A29" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="68">
+      <c r="A30" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="34">
+      <c r="A31" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="51">
+      <c r="A32" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="34">
+      <c r="A33" s="2">
         <v>2019</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="34">
-      <c r="A30" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="51">
-      <c r="A31" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="51">
-      <c r="A32" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="51">
-      <c r="A33" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="51">
+    <row r="34" spans="1:9" ht="34">
       <c r="A34" s="2">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="68">
+    <row r="35" spans="1:9" ht="51">
       <c r="A35" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="2" t="s">
@@ -2198,23 +2195,23 @@
         <v>52</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="34">
+    <row r="37" spans="1:9" ht="51">
       <c r="A37" s="2">
         <v>2015</v>
       </c>
@@ -2225,16 +2222,16 @@
         <v>52</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="2" t="s">
@@ -2243,7 +2240,7 @@
     </row>
     <row r="38" spans="1:9" ht="51">
       <c r="A38" s="2">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>52</v>
@@ -2252,241 +2249,241 @@
         <v>52</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>126</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="H38" s="4"/>
       <c r="I38" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="51">
+    <row r="39" spans="1:9" ht="68">
       <c r="A39" s="2">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="34">
+    <row r="40" spans="1:9" ht="51">
       <c r="A40" s="2">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="51">
+    <row r="41" spans="1:9" ht="34">
       <c r="A41" s="2">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>135</v>
+        <v>52</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="H41" s="4"/>
       <c r="I41" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="51">
       <c r="A42" s="2">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>62</v>
+        <v>52</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="34">
-      <c r="A43" s="12">
-        <v>2025</v>
+    <row r="43" spans="1:9" ht="51">
+      <c r="A43" s="2">
+        <v>2022</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H43" s="12"/>
-      <c r="I43" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="34">
-      <c r="A44" s="12">
-        <v>2025</v>
+      <c r="A44" s="2">
+        <v>2022</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>52</v>
+        <v>38</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H44" s="12"/>
-      <c r="I44" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="34">
-      <c r="A45" s="12">
-        <v>2025</v>
+        <v>155</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="51">
+      <c r="A45" s="2">
+        <v>2019</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H45" s="12"/>
-      <c r="I45" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="51">
-      <c r="A46" s="12">
-        <v>2025</v>
+      <c r="A46" s="2">
+        <v>2014</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H46" s="12"/>
-      <c r="I46" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2495,22 +2492,22 @@
         <v>2025</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="13" t="s">
@@ -2519,52 +2516,52 @@
     </row>
     <row r="48" spans="1:9" ht="34">
       <c r="A48" s="12">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="51">
+    <row r="49" spans="1:9" ht="34">
       <c r="A49" s="12">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="13" t="s">
@@ -2573,25 +2570,25 @@
     </row>
     <row r="50" spans="1:9" ht="51">
       <c r="A50" s="12">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="13" t="s">
@@ -2600,7 +2597,7 @@
     </row>
     <row r="51" spans="1:9" ht="34">
       <c r="A51" s="12">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>52</v>
@@ -2609,16 +2606,16 @@
         <v>52</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="13" t="s">
@@ -2627,7 +2624,7 @@
     </row>
     <row r="52" spans="1:9" ht="34">
       <c r="A52" s="12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>38</v>
@@ -2636,46 +2633,46 @@
         <v>38</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="34">
-      <c r="A53" s="14">
-        <v>2018</v>
+    <row r="53" spans="1:9" ht="51">
+      <c r="A53" s="12">
+        <v>2024</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H53" s="12"/>
+      <c r="I53" s="13" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2684,138 +2681,246 @@
         <v>2024</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>199</v>
+        <v>183</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="H54" s="12"/>
-      <c r="I54" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="51">
+      <c r="I54" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="34">
       <c r="A55" s="12">
         <v>2024</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>196</v>
+        <v>52</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>199</v>
+        <v>186</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="H55" s="12"/>
-      <c r="I55" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="51">
+      <c r="I55" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="34">
       <c r="A56" s="12">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="H56" s="12"/>
-      <c r="I56" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="51">
+      <c r="I56" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="34">
       <c r="A57" s="14">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>196</v>
+        <v>52</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="G57" s="15"/>
+        <v>193</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>194</v>
+      </c>
       <c r="H57" s="14"/>
       <c r="I57" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="51">
-      <c r="A58" s="14">
+      <c r="A58" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H58" s="12"/>
+      <c r="I58" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="51">
+      <c r="A59" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H59" s="12"/>
+      <c r="I59" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="51">
+      <c r="A60" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H60" s="12"/>
+      <c r="I60" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="51">
+      <c r="A61" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G61" s="15"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="51">
+      <c r="A62" s="14">
         <v>2025</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C62" t="s">
         <v>207</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E62" t="s">
         <v>204</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F62" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="H58" s="14"/>
-      <c r="I58" s="16"/>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="D59" s="2"/>
-      <c r="E59" s="4"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="E60" s="4"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="16"/>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="D63" s="2"/>
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="E64" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C2:C9 C29:C31 B12:B42 B54:B57" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B58:B61 C33:C35 B16:B46 C2:C9" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H24" r:id="rId1" xr:uid="{BDF92706-657D-D349-9948-227810B878A1}"/>
+    <hyperlink ref="H28" r:id="rId1" xr:uid="{BDF92706-657D-D349-9948-227810B878A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E83072B-B24D-A446-A7F4-332781774811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E421EB5-6D6A-3240-8D87-8698A9DC5541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31280" yWindow="-4140" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7160" yWindow="2240" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="218">
   <si>
     <t>Year</t>
   </si>
@@ -884,7 +884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -920,9 +920,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1462,7 +1459,9 @@
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="10"/>
+      <c r="I7" s="7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="51">
       <c r="A8" s="4" t="s">
@@ -1482,7 +1481,9 @@
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="10"/>
+      <c r="I8" s="7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="34">
       <c r="A9" s="4" t="s">
@@ -1559,7 +1560,7 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="17"/>
+      <c r="G12" s="4"/>
       <c r="H12" s="9"/>
       <c r="I12" s="10"/>
     </row>
@@ -1570,7 +1571,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="17"/>
+      <c r="G13" s="4"/>
       <c r="H13" s="9"/>
       <c r="I13" s="10"/>
     </row>
@@ -1581,7 +1582,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="17"/>
+      <c r="G14" s="4"/>
       <c r="H14" s="9"/>
       <c r="I14" s="10"/>
     </row>
@@ -1608,7 +1609,9 @@
         <v>213</v>
       </c>
       <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
+      <c r="I15" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="68">
       <c r="A16" s="4">

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E421EB5-6D6A-3240-8D87-8698A9DC5541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8EEC33-87A5-164A-8F1B-BAA13FC9FFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7160" yWindow="2240" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -717,16 +717,26 @@
     <t>Houston, Texas, 25–29 January 2026</t>
   </si>
   <si>
-    <t>Dixit A., Musselman K. N., Addor N., Carr S., Gutmann E., Huang L., Minder J. R., Newman A. J., Petach T., Rahimi S., Vano J. A., Lehner F.</t>
-  </si>
-  <si>
     <t>Resolving snow refugia delays climate change emergence in mountain snowpack</t>
   </si>
   <si>
-    <t>Kwong A., Dixit A., Shields C. A., Lehner F.</t>
-  </si>
-  <si>
     <t>Competing influences of external forcing and sea surface temperature trends on North Pacific atmospheric rivers</t>
+  </si>
+  <si>
+    <r>
+      <t>Dixit, A.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, Musselman, K. N., Addor, N., Carr, S., Gutmann, E., Huang, L., Minder, J. R., Newman, A. J., Petach, T., Rahimi, S., Vano, J. A., &amp; Lehner, F.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kwong, A., Dixit, A., Shields, C. A., &amp; Lehner, F.</t>
   </si>
 </sst>
 </file>
@@ -1452,10 +1462,10 @@
         <v>15</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1463,7 +1473,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="51">
+    <row r="8" spans="1:9" ht="68">
       <c r="A8" s="4" t="s">
         <v>106</v>
       </c>
@@ -1474,10 +1484,10 @@
         <v>15</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -2917,7 +2927,7 @@
       <c r="E64" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" sqref="B58:B61 C33:C35 B16:B46 C2:C9" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8EEC33-87A5-164A-8F1B-BAA13FC9FFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39F0912-2B23-6C4F-A354-B0A61A937BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7160" yWindow="2240" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="217">
   <si>
     <t>Year</t>
   </si>
@@ -706,9 +706,6 @@
   </si>
   <si>
     <t>La Niña- and El Niño-like Long-Term Sea Surface Temperature Trends Modulate Atmospheric River Activity in Western North America</t>
-  </si>
-  <si>
-    <t>Kwong A., Dixit A., Lehner F.</t>
   </si>
   <si>
     <t>106th Annual Meeting of the American Meteorological Society (AMS)</t>
@@ -1462,10 +1459,10 @@
         <v>15</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1484,10 +1481,10 @@
         <v>15</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1610,13 +1607,13 @@
         <v>210</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="4" t="s">
